--- a/artfynd/A 15556-2022 artfynd.xlsx
+++ b/artfynd/A 15556-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15556-2022 artfynd.xlsx
+++ b/artfynd/A 15556-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103327596</v>
+        <v>103327588</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676952.4582619147</v>
+        <v>676746</v>
       </c>
       <c r="R2" t="n">
-        <v>6693971.856699687</v>
+        <v>6694001</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,21 +743,11 @@
           <t>2022-09-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,17 +759,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,53 +791,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103327589</v>
+        <v>69511050</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Simundö, Upl</t>
+          <t>Johannisfors SO om Forsmark, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676628.887957159</v>
+        <v>676735</v>
       </c>
       <c r="R3" t="n">
-        <v>6694099.900877885</v>
+        <v>6693908</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +865,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-10-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3 ex. i äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,73 +886,78 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Lilja, sonja Preuss</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103327592</v>
+        <v>69506429</v>
       </c>
       <c r="B4" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3884</v>
+        <v>3611</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Simundö, Upl</t>
+          <t>Johannisfors SO om Forsmark, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676637.6710521182</v>
+        <v>676727</v>
       </c>
       <c r="R4" t="n">
-        <v>6694092.890824876</v>
+        <v>6693901</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +981,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-10-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 ex. i medelåldrig granskog.  Sporer 13-15 x 8-9 μm, kraftigt vårtiga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,49 +1003,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Lilja, sonja Preuss</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103327597</v>
+        <v>69510614</v>
       </c>
       <c r="B5" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,37 +1034,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Simundö, Upl</t>
+          <t>Johannisfors SO om Forsmark, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676979.261082783</v>
+        <v>676744</v>
       </c>
       <c r="R5" t="n">
-        <v>6694043.566919898</v>
+        <v>6693907</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,22 +1097,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-10-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-10-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 ex. i äldre granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,35 +1118,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103327598</v>
+        <v>102094791</v>
       </c>
       <c r="B6" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>3884</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1209,13 +1174,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677020.7416290885</v>
+        <v>677081</v>
       </c>
       <c r="R6" t="n">
-        <v>6694017.821727781</v>
+        <v>6693800</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1204,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,6 +1220,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1285,15 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103327595</v>
+        <v>103327591</v>
       </c>
       <c r="B7" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>3884</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676682.402662496</v>
+        <v>676625</v>
       </c>
       <c r="R7" t="n">
-        <v>6693887.816923342</v>
+        <v>6694093</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1358,21 +1323,11 @@
           <t>2022-09-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-02</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1381,6 +1336,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1401,15 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103327591</v>
+        <v>103327592</v>
       </c>
       <c r="B8" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676624.7655114855</v>
+        <v>676638</v>
       </c>
       <c r="R8" t="n">
-        <v>6694092.759417721</v>
+        <v>6694093</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1474,19 +1439,9 @@
           <t>2022-09-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,37 +1487,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103327593</v>
+        <v>103327596</v>
       </c>
       <c r="B9" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1572,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676639.3004633632</v>
+        <v>676952</v>
       </c>
       <c r="R9" t="n">
-        <v>6694038.92799873</v>
+        <v>6693972</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1605,21 +1555,11 @@
           <t>2022-09-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-02</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1628,6 +1568,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1645,6 +1600,859 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>99317279</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>FM-150-2-43, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>676802</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6693829</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2013-05-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2013-05-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>99317281</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>FM-150-2-43, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>676802</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6693829</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2013-05-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2013-05-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>103327595</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Simundö, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>676682</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6693888</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Lilja, sonja Preuss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>103327597</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Simundö, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>676980</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6694043</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>103327598</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Simundö, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>677020</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6694018</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>103327593</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Simundö, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>676640</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6694039</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Lilja, sonja Preuss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103327589</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Simundö, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>676629</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6694100</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johan Lilja, sonja Preuss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>69562545</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Johannisfors SO om Forsmark, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>676721</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6693937</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2006-10-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2006-10-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 ex. i äldre granskog med inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog med inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15556-2022 artfynd.xlsx
+++ b/artfynd/A 15556-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327588</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69511050</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506429</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510614</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102094791</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327591</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327592</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327596</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99317279</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99317281</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1933,6 +1988,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327595</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2034,6 +2094,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327597</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2135,6 +2200,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327598</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2236,6 +2306,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327593</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327589</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2453,8 +2533,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69562545</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>